--- a/erp-server/erp-server-file/src/main/resources/excel/wms/poInStockNotField.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/poInStockNotField.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>入库单号</t>
   </si>
@@ -35,6 +35,12 @@
     <t>采购单号</t>
   </si>
   <si>
+    <t>采购订单类型</t>
+  </si>
+  <si>
+    <t>退货方式</t>
+  </si>
+  <si>
     <t>供应商</t>
   </si>
   <si>
@@ -90,6 +96,12 @@
   </si>
   <si>
     <t>{.purchaseOrderCode}</t>
+  </si>
+  <si>
+    <t>{.purchaseTypeName}</t>
+  </si>
+  <si>
+    <t>{.returnModeName}</t>
   </si>
   <si>
     <t>{.supplierName}</t>
@@ -1330,13 +1342,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="19" width="30" customWidth="1"/>
+    <col min="1" max="21" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:19">
+    <row r="1" ht="15" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1394,64 +1406,76 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S2" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="T2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/poInStockNotField.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/poInStockNotField.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="采购入库单数据" sheetId="1" r:id="rId1"/>
@@ -27,11 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>入库单号</t>
   </si>
   <si>
+    <t>委外订单</t>
+  </si>
+  <si>
     <t>采购单号</t>
   </si>
   <si>
@@ -62,10 +65,16 @@
     <t>采购数量</t>
   </si>
   <si>
-    <t>实收数量</t>
-  </si>
-  <si>
-    <t>超收数量</t>
+    <t>入库数量</t>
+  </si>
+  <si>
+    <t>赠品数量</t>
+  </si>
+  <si>
+    <t>采购组织</t>
+  </si>
+  <si>
+    <t>收料组织</t>
   </si>
   <si>
     <t>交货仓库</t>
@@ -95,6 +104,9 @@
     <t>{.code}</t>
   </si>
   <si>
+    <t>{.subcontractCode}</t>
+  </si>
+  <si>
     <t>{.purchaseOrderCode}</t>
   </si>
   <si>
@@ -129,6 +141,12 @@
   </si>
   <si>
     <t>{.exceedQty}</t>
+  </si>
+  <si>
+    <t>{.purchaseOrgName}</t>
+  </si>
+  <si>
+    <t>{.receiveOrgName}</t>
   </si>
   <si>
     <t>{.deliveryWarehouseName}</t>
@@ -1342,13 +1360,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="21" width="30" customWidth="1"/>
+    <col min="1" max="24" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:21">
+    <row r="1" ht="15" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1412,70 +1430,88 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="P2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="Q2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="R2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="T2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="U2" t="s">
-        <v>41</v>
+        <v>44</v>
+      </c>
+      <c r="V2" t="s">
+        <v>45</v>
+      </c>
+      <c r="W2" t="s">
+        <v>46</v>
+      </c>
+      <c r="X2" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/poInStockNotField.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/poInStockNotField.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>入库单号</t>
   </si>
@@ -53,6 +53,12 @@
     <t>作废状态</t>
   </si>
   <si>
+    <t>来源单号</t>
+  </si>
+  <si>
+    <t>发货单</t>
+  </si>
+  <si>
     <t>SKU</t>
   </si>
   <si>
@@ -123,6 +129,12 @@
   </si>
   <si>
     <t>{.invalidStatusName}</t>
+  </si>
+  <si>
+    <t>{.sourceCode}</t>
+  </si>
+  <si>
+    <t>{.deliveryCode}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -1100,6 +1112,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1360,13 +1379,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="24" width="30" customWidth="1"/>
+    <col min="1" max="26" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:24">
+    <row r="1" ht="15" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1439,79 +1458,91 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="U2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="W2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="X2" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
